--- a/Data/Exp 2 Ionic Strength NaCl Data/TEMPEST_Ionic_Strength_NaCl_chem_L2.xlsx
+++ b/Data/Exp 2 Ionic Strength NaCl Data/TEMPEST_Ionic_Strength_NaCl_chem_L2.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/myer056/GitHub/tempest_ionic_strength/Data/Exp 2 Ionic Strength NaCl Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C761BD7A-7582-D444-925D-903E4F832BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C9F217C-7D17-F942-BA51-0FC174C716BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4460" yWindow="3660" windowWidth="26840" windowHeight="15940" xr2:uid="{6DB21FE1-031A-D147-BBB1-6B4694CD69FB}"/>
+    <workbookView xWindow="2160" yWindow="760" windowWidth="31880" windowHeight="19940" xr2:uid="{6DB21FE1-031A-D147-BBB1-6B4694CD69FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -47,77 +47,86 @@
     <t>Wash</t>
   </si>
   <si>
-    <t>Cond_uScm</t>
-  </si>
-  <si>
-    <t>Cond_stdev</t>
-  </si>
-  <si>
     <t>pH</t>
   </si>
   <si>
     <t>pH_stdev</t>
   </si>
   <si>
-    <t>doc_mg_l_mean</t>
+    <t>NaCl</t>
   </si>
   <si>
-    <t>doc_mg_l_sd</t>
+    <t>conductivity_uSpercm</t>
   </si>
   <si>
-    <t>Na</t>
+    <t>conductivity_uSpercm_stdev</t>
   </si>
   <si>
-    <t>Na_stdev</t>
+    <t>doc_mgperL</t>
   </si>
   <si>
-    <t>K</t>
+    <t>doc_mgperL_stdev</t>
   </si>
   <si>
-    <t>K_stdev</t>
+    <t>Na_ppm</t>
   </si>
   <si>
-    <t>Ca</t>
+    <t>Na_ppm_stdev</t>
   </si>
   <si>
-    <t>Ca_stdev</t>
+    <t>K_ppm</t>
   </si>
   <si>
-    <t>Mg</t>
+    <t>K_ppm_stdev</t>
   </si>
   <si>
-    <t>Mg_stdev</t>
+    <t>Ca_ppm</t>
   </si>
   <si>
-    <t>Al</t>
+    <t>Ca_ppm_stdev</t>
   </si>
   <si>
-    <t>Al_stdev</t>
+    <t>Mg_ppm</t>
   </si>
   <si>
-    <t>Fe</t>
+    <t>Mg_ppm_stdev</t>
   </si>
   <si>
-    <t>Fe_stdev</t>
+    <t>Al_ppm</t>
   </si>
   <si>
-    <t>S</t>
+    <t>Al_ppm_stdev</t>
   </si>
   <si>
-    <t>S_stdev</t>
+    <t>Fe_ppm</t>
   </si>
   <si>
-    <t>NaCl</t>
+    <t>Fe_ppm_stdev</t>
+  </si>
+  <si>
+    <t>S_ppm</t>
+  </si>
+  <si>
+    <t>S_ppm_stdev</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -143,8 +152,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -479,8 +496,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AD1467C-EE13-7645-ADC5-4DD69AA0CBCF}">
-  <dimension ref="A1:W43"/>
+  <dimension ref="A1:W44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -493,69 +515,69 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
         <v>11</v>
       </c>
+      <c r="L1" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
         <v>13</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
         <v>15</v>
       </c>
+      <c r="P1" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="Q1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" t="s">
         <v>21</v>
       </c>
+      <c r="V1" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="W1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -566,7 +588,7 @@
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -574,10 +596,70 @@
       <c r="C3">
         <v>1</v>
       </c>
+      <c r="D3" s="2">
+        <v>19.403333333333332</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.94299169314121378</v>
+      </c>
+      <c r="F3" s="2">
+        <v>5.6233333333333322</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.13051181300301254</v>
+      </c>
+      <c r="H3" s="2">
+        <v>18.04</v>
+      </c>
+      <c r="I3" s="2">
+        <v>4.5950081610373674</v>
+      </c>
+      <c r="J3">
+        <v>1.7410080542729487</v>
+      </c>
+      <c r="K3">
+        <v>0.2750111925479673</v>
+      </c>
+      <c r="L3">
+        <v>6.3803456215799423</v>
+      </c>
+      <c r="M3">
+        <v>7.4882489203885599E-2</v>
+      </c>
+      <c r="N3">
+        <v>0.13254004798487753</v>
+      </c>
+      <c r="O3">
+        <v>1.580626522456419E-2</v>
+      </c>
+      <c r="P3">
+        <v>1.5539049375370242</v>
+      </c>
+      <c r="Q3">
+        <v>0.16500886223483402</v>
+      </c>
+      <c r="R3">
+        <v>10.719424926861045</v>
+      </c>
+      <c r="S3">
+        <v>1.0315260822691816</v>
+      </c>
+      <c r="T3">
+        <v>14.895420658939896</v>
+      </c>
+      <c r="U3">
+        <v>1.9347631105544092</v>
+      </c>
+      <c r="V3">
+        <v>0.43894389438943887</v>
+      </c>
+      <c r="W3">
+        <v>7.9413923534758346E-2</v>
+      </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -585,10 +667,64 @@
       <c r="C4">
         <v>2</v>
       </c>
+      <c r="D4" s="2">
+        <v>11.526666666666666</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0.4366157731156004</v>
+      </c>
+      <c r="F4" s="2">
+        <v>5.9866666666666672</v>
+      </c>
+      <c r="G4" s="2">
+        <v>9.8657657246324679E-2</v>
+      </c>
+      <c r="H4" s="2">
+        <v>13.076666666666668</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0.97725806895278822</v>
+      </c>
+      <c r="J4">
+        <v>1.3010863555535632</v>
+      </c>
+      <c r="K4">
+        <v>0.12473604237431216</v>
+      </c>
+      <c r="L4">
+        <v>5.8792092410000159</v>
+      </c>
+      <c r="M4">
+        <v>1.2705403658941923</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>1.5548401418042876</v>
+      </c>
+      <c r="Q4">
+        <v>9.5082921642807725E-2</v>
+      </c>
+      <c r="R4">
+        <v>10.998831281837141</v>
+      </c>
+      <c r="S4">
+        <v>0.62727220028533759</v>
+      </c>
+      <c r="T4">
+        <v>15.493410583680868</v>
+      </c>
+      <c r="U4">
+        <v>1.0178693201582911</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -596,10 +732,64 @@
       <c r="C5">
         <v>3</v>
       </c>
+      <c r="D5" s="2">
+        <v>11.950000000000001</v>
+      </c>
+      <c r="E5" s="2">
+        <v>4.4349069888781232</v>
+      </c>
+      <c r="F5" s="2">
+        <v>6.19</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0.25119713374160968</v>
+      </c>
+      <c r="H5" s="2">
+        <v>9.2000000000000011</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0.56665686266028803</v>
+      </c>
+      <c r="J5">
+        <v>1.2587976868247635</v>
+      </c>
+      <c r="K5">
+        <v>0.25963061349694022</v>
+      </c>
+      <c r="L5">
+        <v>5.583941994534297</v>
+      </c>
+      <c r="M5">
+        <v>1.8199176492739009</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>1.1818762141565233</v>
+      </c>
+      <c r="Q5">
+        <v>0.19264761341279979</v>
+      </c>
+      <c r="R5">
+        <v>6.1729765005627542</v>
+      </c>
+      <c r="S5">
+        <v>3.7636375843742345</v>
+      </c>
+      <c r="T5">
+        <v>10.951286398711241</v>
+      </c>
+      <c r="U5">
+        <v>2.1995505391430066</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -607,21 +797,129 @@
       <c r="C6">
         <v>4</v>
       </c>
+      <c r="D6" s="2">
+        <v>10.696666666666667</v>
+      </c>
+      <c r="E6" s="2">
+        <v>3.6430801985865338</v>
+      </c>
+      <c r="F6" s="2">
+        <v>6.3433333333333337</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0.28746014216467197</v>
+      </c>
+      <c r="H6" s="2">
+        <v>8.2466666666666679</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.66583281184793897</v>
+      </c>
+      <c r="J6">
+        <v>1.1413457659030797</v>
+      </c>
+      <c r="K6">
+        <v>0.15429766754444463</v>
+      </c>
+      <c r="L6">
+        <v>5.2519101204968131</v>
+      </c>
+      <c r="M6">
+        <v>1.6193431758983383</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>1.1607605627512869</v>
+      </c>
+      <c r="Q6">
+        <v>0.1196447828888946</v>
+      </c>
+      <c r="R6">
+        <v>8.4084754618450486</v>
+      </c>
+      <c r="S6">
+        <v>0.70177221113595134</v>
+      </c>
+      <c r="T6">
+        <v>10.590817504759297</v>
+      </c>
+      <c r="U6">
+        <v>1.2018059214145911</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
         <v>5</v>
+      </c>
+      <c r="D7" s="2">
+        <v>14.856666666666667</v>
+      </c>
+      <c r="E7" s="2">
+        <v>6.14125665750369</v>
+      </c>
+      <c r="F7" s="2">
+        <v>6.3033333333333319</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0.20008331597945242</v>
+      </c>
+      <c r="H7" s="2">
+        <v>7.1099999999999994</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.41904653679513898</v>
+      </c>
+      <c r="J7">
+        <v>1.1160921086056694</v>
+      </c>
+      <c r="K7">
+        <v>0.28478940620148724</v>
+      </c>
+      <c r="L7">
+        <v>5.2708888477079627</v>
+      </c>
+      <c r="M7">
+        <v>2.4430790101121898</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1.0082014261865078</v>
+      </c>
+      <c r="Q7">
+        <v>7.2532235609303108E-2</v>
+      </c>
+      <c r="R7">
+        <v>7.3534629563916818</v>
+      </c>
+      <c r="S7">
+        <v>0.44946529560453652</v>
+      </c>
+      <c r="T7">
+        <v>8.789862385411217</v>
+      </c>
+      <c r="U7">
+        <v>0.69598340804277981</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -629,10 +927,64 @@
       <c r="C8">
         <v>6</v>
       </c>
+      <c r="D8" s="2">
+        <v>6.8999999999999995</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.79018985060553615</v>
+      </c>
+      <c r="F8" s="2">
+        <v>5.7466666666666661</v>
+      </c>
+      <c r="G8" s="2">
+        <v>4.5092497528228866E-2</v>
+      </c>
+      <c r="H8" s="2">
+        <v>7.003333333333333</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.22479620400116501</v>
+      </c>
+      <c r="J8">
+        <v>0.61819159904962562</v>
+      </c>
+      <c r="K8">
+        <v>6.6567635293484098E-2</v>
+      </c>
+      <c r="L8">
+        <v>3.1558790388371647</v>
+      </c>
+      <c r="M8">
+        <v>8.9750982574356861E-2</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1.0483337733521949</v>
+      </c>
+      <c r="Q8">
+        <v>1.3374677833726752E-2</v>
+      </c>
+      <c r="R8">
+        <v>7.6367745276033503</v>
+      </c>
+      <c r="S8">
+        <v>0.13353573594187598</v>
+      </c>
+      <c r="T8">
+        <v>9.2119065177454633</v>
+      </c>
+      <c r="U8">
+        <v>0.18989864693670058</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B9">
         <v>0.1</v>
@@ -640,10 +992,18 @@
       <c r="C9">
         <v>0</v>
       </c>
+      <c r="D9" s="3">
+        <v>91.7</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="3">
+        <v>6.766</v>
+      </c>
+      <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B10">
         <v>0.1</v>
@@ -651,10 +1011,67 @@
       <c r="C10">
         <v>1</v>
       </c>
+      <c r="D10" s="2">
+        <v>104.30000000000001</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0.87177978870813888</v>
+      </c>
+      <c r="F10" s="2">
+        <v>5.4033333333333333</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0.15011106998930263</v>
+      </c>
+      <c r="H10" s="2">
+        <v>10.826666666666666</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0.28536526301099352</v>
+      </c>
+      <c r="J10">
+        <v>15.145320601903736</v>
+      </c>
+      <c r="K10">
+        <v>1.9372206744155949</v>
+      </c>
+      <c r="L10">
+        <v>7.0598948182323582</v>
+      </c>
+      <c r="M10">
+        <v>0.59087365776094047</v>
+      </c>
+      <c r="N10">
+        <v>0.71961967541542482</v>
+      </c>
+      <c r="O10">
+        <v>1.4707747044483854E-2</v>
+      </c>
+      <c r="P10">
+        <v>1.306211096093552</v>
+      </c>
+      <c r="Q10">
+        <v>3.1766296116945966E-2</v>
+      </c>
+      <c r="R10">
+        <v>6.6860161925935726</v>
+      </c>
+      <c r="S10">
+        <v>0.1682079669580139</v>
+      </c>
+      <c r="T10">
+        <v>9.1615522135904595</v>
+      </c>
+      <c r="U10">
+        <v>0.59410575896531492</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B11">
         <v>0.1</v>
@@ -662,10 +1079,67 @@
       <c r="C11">
         <v>2</v>
       </c>
+      <c r="D11" s="2">
+        <v>20.766666666666669</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2.2579267776731231</v>
+      </c>
+      <c r="F11" s="2">
+        <v>5.9233333333333329</v>
+      </c>
+      <c r="G11" s="2">
+        <v>5.6862407030773041E-2</v>
+      </c>
+      <c r="H11" s="2">
+        <v>16.510000000000002</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0.53357286287816452</v>
+      </c>
+      <c r="J11">
+        <v>5.0275698211323796</v>
+      </c>
+      <c r="K11">
+        <v>0.26806379114536383</v>
+      </c>
+      <c r="L11">
+        <v>5.87047604441576</v>
+      </c>
+      <c r="M11">
+        <v>0.56542723458389077</v>
+      </c>
+      <c r="N11">
+        <v>0.21212708722099713</v>
+      </c>
+      <c r="O11">
+        <v>3.5458076880651446E-2</v>
+      </c>
+      <c r="P11">
+        <v>2.0205298352490573</v>
+      </c>
+      <c r="Q11">
+        <v>0.22012326729676104</v>
+      </c>
+      <c r="R11">
+        <v>13.660052752247687</v>
+      </c>
+      <c r="S11">
+        <v>1.7213858699134743</v>
+      </c>
+      <c r="T11">
+        <v>20.247227389356564</v>
+      </c>
+      <c r="U11">
+        <v>2.4214107877206836</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B12">
         <v>0.1</v>
@@ -673,10 +1147,67 @@
       <c r="C12">
         <v>3</v>
       </c>
+      <c r="D12" s="2">
+        <v>12.28</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.19974984355438122</v>
+      </c>
+      <c r="F12" s="2">
+        <v>6.0266666666666664</v>
+      </c>
+      <c r="G12" s="2">
+        <v>6.1101009266077921E-2</v>
+      </c>
+      <c r="H12" s="2">
+        <v>12.656666666666666</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0.37753587026047392</v>
+      </c>
+      <c r="J12">
+        <v>3.9569044096770813</v>
+      </c>
+      <c r="K12">
+        <v>4.7984459464126557E-2</v>
+      </c>
+      <c r="L12">
+        <v>4.9830341680991248</v>
+      </c>
+      <c r="M12">
+        <v>6.9599169190531454E-2</v>
+      </c>
+      <c r="N12">
+        <v>0.15671828676215174</v>
+      </c>
+      <c r="O12">
+        <v>4.5244687221683783E-3</v>
+      </c>
+      <c r="P12">
+        <v>1.7070393823448675</v>
+      </c>
+      <c r="Q12">
+        <v>7.8977688409891542E-2</v>
+      </c>
+      <c r="R12">
+        <v>11.797318547330022</v>
+      </c>
+      <c r="S12">
+        <v>0.51974440883688122</v>
+      </c>
+      <c r="T12">
+        <v>16.333977230986537</v>
+      </c>
+      <c r="U12">
+        <v>0.98797436904643832</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B13">
         <v>0.1</v>
@@ -684,10 +1215,67 @@
       <c r="C13">
         <v>4</v>
       </c>
+      <c r="D13" s="2">
+        <v>9.6233333333333348</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0.83050185630938445</v>
+      </c>
+      <c r="F13" s="2">
+        <v>6.1266666666666678</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0.13316656236958774</v>
+      </c>
+      <c r="H13" s="2">
+        <v>9.92</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1.2920139318134167</v>
+      </c>
+      <c r="J13">
+        <v>3.213490533614261</v>
+      </c>
+      <c r="K13">
+        <v>0.2888573984229113</v>
+      </c>
+      <c r="L13">
+        <v>4.2370061750089993</v>
+      </c>
+      <c r="M13">
+        <v>0.28934310469826113</v>
+      </c>
+      <c r="N13">
+        <v>0.10028354700336865</v>
+      </c>
+      <c r="O13">
+        <v>2.7069638294280041E-2</v>
+      </c>
+      <c r="P13">
+        <v>0.93866662463501427</v>
+      </c>
+      <c r="Q13">
+        <v>0.66665640108775837</v>
+      </c>
+      <c r="R13">
+        <v>10.025968559902806</v>
+      </c>
+      <c r="S13">
+        <v>1.2180962448878672</v>
+      </c>
+      <c r="T13">
+        <v>13.389113957792567</v>
+      </c>
+      <c r="U13">
+        <v>2.1707355892143116</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B14">
         <v>0.1</v>
@@ -695,10 +1283,64 @@
       <c r="C14">
         <v>5</v>
       </c>
+      <c r="D14" s="2">
+        <v>8.6066666666666674</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0.15275252316519508</v>
+      </c>
+      <c r="F14" s="2">
+        <v>6.12</v>
+      </c>
+      <c r="G14" s="2">
+        <v>3.4641016151377831E-2</v>
+      </c>
+      <c r="H14" s="2">
+        <v>7.2033333333333331</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0.22722969289539027</v>
+      </c>
+      <c r="J14">
+        <v>2.9912882353820174</v>
+      </c>
+      <c r="K14">
+        <v>7.6947125764528071E-2</v>
+      </c>
+      <c r="L14">
+        <v>3.269304092035112</v>
+      </c>
+      <c r="M14">
+        <v>8.7432518951115173E-2</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0.92010833658421909</v>
+      </c>
+      <c r="Q14">
+        <v>2.3315511739698879E-2</v>
+      </c>
+      <c r="R14">
+        <v>6.8074446841615623</v>
+      </c>
+      <c r="S14">
+        <v>0.13467416276848121</v>
+      </c>
+      <c r="T14">
+        <v>7.8415631916033783</v>
+      </c>
+      <c r="U14">
+        <v>0.16143707806632149</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B15">
         <v>0.1</v>
@@ -706,10 +1348,64 @@
       <c r="C15">
         <v>6</v>
       </c>
+      <c r="D15" s="2">
+        <v>7.61</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0.74839828968270683</v>
+      </c>
+      <c r="F15" s="2">
+        <v>5.9466666666666663</v>
+      </c>
+      <c r="G15" s="2">
+        <v>4.0414518843273822E-2</v>
+      </c>
+      <c r="H15" s="2">
+        <v>6.4433333333333342</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0.54372174256078165</v>
+      </c>
+      <c r="J15">
+        <v>2.4259948297246008</v>
+      </c>
+      <c r="K15">
+        <v>0.12589868015195935</v>
+      </c>
+      <c r="L15">
+        <v>2.8183303406159674</v>
+      </c>
+      <c r="M15">
+        <v>0.25989751465486138</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0.88847820461796534</v>
+      </c>
+      <c r="Q15">
+        <v>6.2087460708704433E-2</v>
+      </c>
+      <c r="R15">
+        <v>6.6322061965078278</v>
+      </c>
+      <c r="S15">
+        <v>0.37590841672461861</v>
+      </c>
+      <c r="T15">
+        <v>7.4869025542334073</v>
+      </c>
+      <c r="U15">
+        <v>0.62707927433479849</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -717,10 +1413,20 @@
       <c r="C16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D16" s="3">
+        <v>728.2</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="3">
+        <v>5.9240000000000004</v>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -728,10 +1434,67 @@
       <c r="C17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D17" s="2">
+        <v>895.4666666666667</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1.361371857110818</v>
+      </c>
+      <c r="F17" s="2">
+        <v>4.8999999999999995</v>
+      </c>
+      <c r="G17" s="2">
+        <v>7.000000000000034E-2</v>
+      </c>
+      <c r="H17" s="2">
+        <v>5.12</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0.30265491900843117</v>
+      </c>
+      <c r="J17" s="4">
+        <v>138.55879122612464</v>
+      </c>
+      <c r="K17" s="4">
+        <v>1.5666310571190565</v>
+      </c>
+      <c r="L17">
+        <v>9.1651703079836331</v>
+      </c>
+      <c r="M17">
+        <v>0.42102902041804691</v>
+      </c>
+      <c r="N17">
+        <v>4.0580503921996307</v>
+      </c>
+      <c r="O17">
+        <v>9.2313557632792184E-2</v>
+      </c>
+      <c r="P17">
+        <v>2.6469262383903982</v>
+      </c>
+      <c r="Q17">
+        <v>4.1597586993901238E-2</v>
+      </c>
+      <c r="R17">
+        <v>1.4328099307777549</v>
+      </c>
+      <c r="S17">
+        <v>2.6358065500811236E-2</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0.58745874587458768</v>
+      </c>
+      <c r="W17">
+        <v>9.9174780206711013E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -739,10 +1502,70 @@
       <c r="C18">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D18" s="2">
+        <v>78.089999999999989</v>
+      </c>
+      <c r="E18" s="2">
+        <v>5.1057614515368828</v>
+      </c>
+      <c r="F18" s="2">
+        <v>5.81</v>
+      </c>
+      <c r="G18" s="2">
+        <v>6.2449979983984001E-2</v>
+      </c>
+      <c r="H18" s="2">
+        <v>19.893333333333331</v>
+      </c>
+      <c r="I18" s="2">
+        <v>1.3992974427666673</v>
+      </c>
+      <c r="J18">
+        <v>16.735553862016406</v>
+      </c>
+      <c r="K18">
+        <v>0.65669770001215721</v>
+      </c>
+      <c r="L18">
+        <v>5.2108001951123928</v>
+      </c>
+      <c r="M18">
+        <v>0.16643865773153646</v>
+      </c>
+      <c r="N18">
+        <v>0.10672192198014369</v>
+      </c>
+      <c r="O18">
+        <v>4.1036803124211575E-2</v>
+      </c>
+      <c r="P18">
+        <v>1.9619495331202856</v>
+      </c>
+      <c r="Q18">
+        <v>0.16648329488722344</v>
+      </c>
+      <c r="R18">
+        <v>14.129142579793074</v>
+      </c>
+      <c r="S18">
+        <v>1.1393615335999421</v>
+      </c>
+      <c r="T18">
+        <v>21.325112453849574</v>
+      </c>
+      <c r="U18">
+        <v>1.9366580118919867</v>
+      </c>
+      <c r="V18">
+        <v>0.45874587458745869</v>
+      </c>
+      <c r="W18">
+        <v>3.0248024389147546E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -750,10 +1573,67 @@
       <c r="C19">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D19" s="2">
+        <v>21.47</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0.49325449820554085</v>
+      </c>
+      <c r="F19" s="2">
+        <v>6.2033333333333331</v>
+      </c>
+      <c r="G19" s="2">
+        <v>4.5092497528228866E-2</v>
+      </c>
+      <c r="H19" s="2">
+        <v>18.976666666666667</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0.13012814197295328</v>
+      </c>
+      <c r="J19">
+        <v>6.9807683686735098</v>
+      </c>
+      <c r="K19">
+        <v>7.5561764826966651E-2</v>
+      </c>
+      <c r="L19">
+        <v>5.3823968577532684</v>
+      </c>
+      <c r="M19">
+        <v>0.13797630684573783</v>
+      </c>
+      <c r="N19">
+        <v>0.17835187294509214</v>
+      </c>
+      <c r="O19">
+        <v>2.6794538741712243E-2</v>
+      </c>
+      <c r="P19">
+        <v>2.4434943539669343</v>
+      </c>
+      <c r="Q19">
+        <v>1.3226844568762943E-2</v>
+      </c>
+      <c r="R19">
+        <v>16.910152782468273</v>
+      </c>
+      <c r="S19">
+        <v>8.1022333190220425E-2</v>
+      </c>
+      <c r="T19">
+        <v>24.591253361467295</v>
+      </c>
+      <c r="U19">
+        <v>0.32899380426792135</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -761,10 +1641,67 @@
       <c r="C20">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D20" s="2">
+        <v>14.790000000000001</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0.30446674695276632</v>
+      </c>
+      <c r="F20" s="2">
+        <v>6.3299999999999992</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0.20223748416156673</v>
+      </c>
+      <c r="H20" s="2">
+        <v>14.180000000000001</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0.12529964086141662</v>
+      </c>
+      <c r="J20">
+        <v>5.0842037626455072</v>
+      </c>
+      <c r="K20">
+        <v>0.23900796807120051</v>
+      </c>
+      <c r="L20">
+        <v>4.3915198531118937</v>
+      </c>
+      <c r="M20">
+        <v>0.2841790463005156</v>
+      </c>
+      <c r="N20">
+        <v>0.11908974141482688</v>
+      </c>
+      <c r="O20">
+        <v>1.829813054655488E-2</v>
+      </c>
+      <c r="P20">
+        <v>2.058238794952524</v>
+      </c>
+      <c r="Q20">
+        <v>5.9873794228058851E-2</v>
+      </c>
+      <c r="R20">
+        <v>14.170697532664425</v>
+      </c>
+      <c r="S20">
+        <v>0.34661974752205738</v>
+      </c>
+      <c r="T20">
+        <v>19.790391607130967</v>
+      </c>
+      <c r="U20">
+        <v>0.50941881507602138</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -772,10 +1709,64 @@
       <c r="C21">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D21" s="2">
+        <v>13.31</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0.4956813492557493</v>
+      </c>
+      <c r="F21" s="2">
+        <v>6.3166666666666664</v>
+      </c>
+      <c r="G21" s="2">
+        <v>4.9328828623162443E-2</v>
+      </c>
+      <c r="H21" s="2">
+        <v>11.36</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0.97555112628708562</v>
+      </c>
+      <c r="J21">
+        <v>4.4837943246514547</v>
+      </c>
+      <c r="K21">
+        <v>1.5728520009726504E-2</v>
+      </c>
+      <c r="L21">
+        <v>4.0862200808140186</v>
+      </c>
+      <c r="M21">
+        <v>0.27992653884257651</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>1.6953703448303041</v>
+      </c>
+      <c r="Q21">
+        <v>0.12855092082589922</v>
+      </c>
+      <c r="R21">
+        <v>11.734543814526708</v>
+      </c>
+      <c r="S21">
+        <v>0.85126057047575165</v>
+      </c>
+      <c r="T21">
+        <v>15.966445805775452</v>
+      </c>
+      <c r="U21">
+        <v>1.4022768730732202</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -783,10 +1774,64 @@
       <c r="C22">
         <v>6</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D22" s="2">
+        <v>12.763333333333334</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1.0826048832946087</v>
+      </c>
+      <c r="F22" s="2">
+        <v>6.2233333333333336</v>
+      </c>
+      <c r="G22" s="2">
+        <v>5.507570547286119E-2</v>
+      </c>
+      <c r="H22" s="2">
+        <v>9.6066666666666674</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0.58620246786697661</v>
+      </c>
+      <c r="J22">
+        <v>3.7740021816769023</v>
+      </c>
+      <c r="K22">
+        <v>6.3150543037214235E-2</v>
+      </c>
+      <c r="L22">
+        <v>4.7853657185823257</v>
+      </c>
+      <c r="M22">
+        <v>1.174800195338457</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>1.465069726570966</v>
+      </c>
+      <c r="Q22">
+        <v>6.8186214036562609E-2</v>
+      </c>
+      <c r="R22">
+        <v>10.286032227833644</v>
+      </c>
+      <c r="S22">
+        <v>0.39622333936233267</v>
+      </c>
+      <c r="T22">
+        <v>13.713517630642498</v>
+      </c>
+      <c r="U22">
+        <v>0.7455383193784002</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B23">
         <v>5</v>
@@ -794,10 +1839,20 @@
       <c r="C23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D23" s="3">
+        <v>3425</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" s="3">
+        <v>5.6829999999999998</v>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B24">
         <v>5</v>
@@ -805,10 +1860,67 @@
       <c r="C24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D24" s="2">
+        <v>4133.333333333333</v>
+      </c>
+      <c r="E24" s="2">
+        <v>11.547005383792516</v>
+      </c>
+      <c r="F24" s="2">
+        <v>4.5933333333333337</v>
+      </c>
+      <c r="G24" s="2">
+        <v>3.7859388972002035E-2</v>
+      </c>
+      <c r="H24" s="2">
+        <v>5.3500000000000005</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0.19467922333931789</v>
+      </c>
+      <c r="J24">
+        <v>762.15409795667949</v>
+      </c>
+      <c r="K24">
+        <v>5.308428266875481</v>
+      </c>
+      <c r="L24">
+        <v>13.316364164478637</v>
+      </c>
+      <c r="M24">
+        <v>0.39777860212769822</v>
+      </c>
+      <c r="N24">
+        <v>12.788931165127758</v>
+      </c>
+      <c r="O24">
+        <v>0.21852550539415616</v>
+      </c>
+      <c r="P24">
+        <v>7.5515062639244119</v>
+      </c>
+      <c r="Q24">
+        <v>5.341630882182799E-2</v>
+      </c>
+      <c r="R24">
+        <v>1.6381358440696474</v>
+      </c>
+      <c r="S24">
+        <v>1.9282121678266345E-2</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0.50165016501650184</v>
+      </c>
+      <c r="W24">
+        <v>3.0248024389147511E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B25">
         <v>5</v>
@@ -816,10 +1928,67 @@
       <c r="C25">
         <v>2</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D25" s="2">
+        <v>326.06666666666666</v>
+      </c>
+      <c r="E25" s="2">
+        <v>6.6665833328124773</v>
+      </c>
+      <c r="F25" s="2">
+        <v>5.6566666666666663</v>
+      </c>
+      <c r="G25" s="2">
+        <v>9.2915732431775561E-2</v>
+      </c>
+      <c r="H25" s="2">
+        <v>22.036666666666665</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0.87271606684724867</v>
+      </c>
+      <c r="J25">
+        <v>62.530488798136012</v>
+      </c>
+      <c r="K25">
+        <v>1.2107229181468033</v>
+      </c>
+      <c r="L25">
+        <v>5.7246102632896507</v>
+      </c>
+      <c r="M25">
+        <v>0.10871534765758667</v>
+      </c>
+      <c r="N25">
+        <v>0.17710782056564001</v>
+      </c>
+      <c r="O25">
+        <v>1.0691277126329326E-2</v>
+      </c>
+      <c r="P25">
+        <v>2.1649923877251576</v>
+      </c>
+      <c r="Q25">
+        <v>5.5917952216248838E-2</v>
+      </c>
+      <c r="R25">
+        <v>15.47472690653143</v>
+      </c>
+      <c r="S25">
+        <v>0.30390419947629171</v>
+      </c>
+      <c r="T25">
+        <v>24.634670561830877</v>
+      </c>
+      <c r="U25">
+        <v>0.61600952243103502</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B26">
         <v>5</v>
@@ -827,10 +1996,67 @@
       <c r="C26">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D26" s="2">
+        <v>43.013333333333328</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0.36226141573914949</v>
+      </c>
+      <c r="F26" s="2">
+        <v>6.3166666666666664</v>
+      </c>
+      <c r="G26" s="2">
+        <v>2.3094010767585053E-2</v>
+      </c>
+      <c r="H26" s="2">
+        <v>28.81</v>
+      </c>
+      <c r="I26" s="2">
+        <v>1.0923369443537108</v>
+      </c>
+      <c r="J26">
+        <v>12.716337173682399</v>
+      </c>
+      <c r="K26">
+        <v>0.15826745469856277</v>
+      </c>
+      <c r="L26">
+        <v>7.5696060783257098</v>
+      </c>
+      <c r="M26">
+        <v>0.2922402240813104</v>
+      </c>
+      <c r="N26">
+        <v>0.27363497564403949</v>
+      </c>
+      <c r="O26">
+        <v>2.4208586763645207E-2</v>
+      </c>
+      <c r="P26">
+        <v>3.7600134947951567</v>
+      </c>
+      <c r="Q26">
+        <v>0.1280531674893865</v>
+      </c>
+      <c r="R26">
+        <v>25.074784051025162</v>
+      </c>
+      <c r="S26">
+        <v>0.86497111394963977</v>
+      </c>
+      <c r="T26">
+        <v>37.235750754287167</v>
+      </c>
+      <c r="U26">
+        <v>1.1041850480288531</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B27">
         <v>5</v>
@@ -838,10 +2064,67 @@
       <c r="C27">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D27" s="2">
+        <v>23.429999999999996</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0.14730919862656211</v>
+      </c>
+      <c r="F27" s="2">
+        <v>6.543333333333333</v>
+      </c>
+      <c r="G27" s="2">
+        <v>2.0816659994661382E-2</v>
+      </c>
+      <c r="H27" s="2">
+        <v>21.313333333333333</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0.86222580182533182</v>
+      </c>
+      <c r="J27">
+        <v>8.5559092063776685</v>
+      </c>
+      <c r="K27">
+        <v>0.16089127709744211</v>
+      </c>
+      <c r="L27">
+        <v>6.8912788408987558</v>
+      </c>
+      <c r="M27">
+        <v>0.19711201371208686</v>
+      </c>
+      <c r="N27">
+        <v>0.2024089377893028</v>
+      </c>
+      <c r="O27">
+        <v>1.0368042785776922E-2</v>
+      </c>
+      <c r="P27">
+        <v>3.1872068619317169</v>
+      </c>
+      <c r="Q27">
+        <v>0.10418133201384505</v>
+      </c>
+      <c r="R27">
+        <v>20.996411390597832</v>
+      </c>
+      <c r="S27">
+        <v>0.62386179423781407</v>
+      </c>
+      <c r="T27">
+        <v>30.594771565874812</v>
+      </c>
+      <c r="U27">
+        <v>1.1454053303177181</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B28">
         <v>5</v>
@@ -849,10 +2132,64 @@
       <c r="C28">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D28" s="2">
+        <v>19.936666666666667</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0.20792626898334288</v>
+      </c>
+      <c r="F28" s="2">
+        <v>6.7266666666666666</v>
+      </c>
+      <c r="G28" s="2">
+        <v>2.5166114784235766E-2</v>
+      </c>
+      <c r="H28" s="2">
+        <v>13.966666666666667</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0.5444569159569318</v>
+      </c>
+      <c r="J28">
+        <v>7.2951689305300276</v>
+      </c>
+      <c r="K28">
+        <v>3.3010487548871335E-2</v>
+      </c>
+      <c r="L28">
+        <v>5.9920657669949664</v>
+      </c>
+      <c r="M28">
+        <v>1.5989085609836806</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>2.0411640931863491</v>
+      </c>
+      <c r="Q28">
+        <v>0.10838899546689441</v>
+      </c>
+      <c r="R28">
+        <v>13.753076729041465</v>
+      </c>
+      <c r="S28">
+        <v>0.69789337029062282</v>
+      </c>
+      <c r="T28">
+        <v>19.014680608901738</v>
+      </c>
+      <c r="U28">
+        <v>1.1398319951577047</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B29">
         <v>5</v>
@@ -860,10 +2197,64 @@
       <c r="C29">
         <v>6</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D29" s="2">
+        <v>17.616666666666671</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0.98561317631884915</v>
+      </c>
+      <c r="F29" s="2">
+        <v>6.63</v>
+      </c>
+      <c r="G29" s="2">
+        <v>3.4641016151377831E-2</v>
+      </c>
+      <c r="H29" s="2">
+        <v>11.943333333333333</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0.24337899115029105</v>
+      </c>
+      <c r="J29">
+        <v>6.5039374785194495</v>
+      </c>
+      <c r="K29">
+        <v>0.17517196604898552</v>
+      </c>
+      <c r="L29">
+        <v>4.5809876514899637</v>
+      </c>
+      <c r="M29">
+        <v>0.43831248556767599</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>1.6454427742552926</v>
+      </c>
+      <c r="Q29">
+        <v>4.2433990328734406E-2</v>
+      </c>
+      <c r="R29">
+        <v>11.38023713821474</v>
+      </c>
+      <c r="S29">
+        <v>0.23285680088158067</v>
+      </c>
+      <c r="T29">
+        <v>15.158673617144407</v>
+      </c>
+      <c r="U29">
+        <v>0.44833414858832571</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B30">
         <v>25</v>
@@ -871,10 +2262,20 @@
       <c r="C30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D30" s="3">
+        <v>15580</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" s="3">
+        <v>5.5970000000000004</v>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B31">
         <v>25</v>
@@ -882,10 +2283,70 @@
       <c r="C31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D31" s="2">
+        <v>18566.666666666668</v>
+      </c>
+      <c r="E31" s="2">
+        <v>30.550504633038937</v>
+      </c>
+      <c r="F31" s="2">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="G31" s="2">
+        <v>1.0000000000000231E-2</v>
+      </c>
+      <c r="H31" s="2">
+        <v>5.8066666666666658</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0.44836740886613646</v>
+      </c>
+      <c r="J31">
+        <v>3968.5228955409943</v>
+      </c>
+      <c r="K31">
+        <v>14.133162201794141</v>
+      </c>
+      <c r="L31">
+        <v>21.343679175695872</v>
+      </c>
+      <c r="M31">
+        <v>0.16744267036470281</v>
+      </c>
+      <c r="N31">
+        <v>25.449521368485815</v>
+      </c>
+      <c r="O31">
+        <v>0.22725712452543195</v>
+      </c>
+      <c r="P31">
+        <v>15.271720048938954</v>
+      </c>
+      <c r="Q31">
+        <v>9.288630853446507E-2</v>
+      </c>
+      <c r="R31">
+        <v>4.7729241164392917</v>
+      </c>
+      <c r="S31">
+        <v>1.9157716576688254E-2</v>
+      </c>
+      <c r="T31">
+        <v>0.16428442364934906</v>
+      </c>
+      <c r="U31">
+        <v>1.8713266216324596E-2</v>
+      </c>
+      <c r="V31">
+        <v>1.3795379537953798</v>
+      </c>
+      <c r="W31">
+        <v>9.6163711447746075E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B32">
         <v>25</v>
@@ -893,10 +2354,67 @@
       <c r="C32">
         <v>2</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D32" s="2">
+        <v>1570</v>
+      </c>
+      <c r="E32" s="2">
+        <v>55.488737596020329</v>
+      </c>
+      <c r="F32" s="2">
+        <v>5.38</v>
+      </c>
+      <c r="G32" s="2">
+        <v>3.4641016151377831E-2</v>
+      </c>
+      <c r="H32" s="2">
+        <v>14.253333333333332</v>
+      </c>
+      <c r="I32" s="2">
+        <v>0.60682232435312788</v>
+      </c>
+      <c r="J32">
+        <v>297.03793340034645</v>
+      </c>
+      <c r="K32">
+        <v>7.984926393560098</v>
+      </c>
+      <c r="L32">
+        <v>4.5591073605680865</v>
+      </c>
+      <c r="M32">
+        <v>0.4537838078092557</v>
+      </c>
+      <c r="N32">
+        <v>4.3452972396578082E-2</v>
+      </c>
+      <c r="O32">
+        <v>1.6779452912320823E-2</v>
+      </c>
+      <c r="P32">
+        <v>1.1129863918449541</v>
+      </c>
+      <c r="Q32">
+        <v>0.23924585439435897</v>
+      </c>
+      <c r="R32">
+        <v>8.4789311724376706</v>
+      </c>
+      <c r="S32">
+        <v>1.6354839497983302</v>
+      </c>
+      <c r="T32">
+        <v>12.85414651144602</v>
+      </c>
+      <c r="U32">
+        <v>2.6394688800422617</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B33">
         <v>25</v>
@@ -904,10 +2422,67 @@
       <c r="C33">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D33" s="2">
+        <v>127.83333333333333</v>
+      </c>
+      <c r="E33" s="2">
+        <v>3.2129944496269132</v>
+      </c>
+      <c r="F33" s="2">
+        <v>6.3133333333333335</v>
+      </c>
+      <c r="G33" s="2">
+        <v>5.7735026918962373E-2</v>
+      </c>
+      <c r="H33" s="2">
+        <v>45.763333333333328</v>
+      </c>
+      <c r="I33" s="2">
+        <v>1.6823891741607602</v>
+      </c>
+      <c r="J33">
+        <v>33.414496340124323</v>
+      </c>
+      <c r="K33">
+        <v>0.55085706253419287</v>
+      </c>
+      <c r="L33">
+        <v>10.243740708042393</v>
+      </c>
+      <c r="M33">
+        <v>0.28792398141569281</v>
+      </c>
+      <c r="N33">
+        <v>0.15473103425991006</v>
+      </c>
+      <c r="O33">
+        <v>2.9076344462090599E-2</v>
+      </c>
+      <c r="P33">
+        <v>5.8222634312278059</v>
+      </c>
+      <c r="Q33">
+        <v>0.14062306579026129</v>
+      </c>
+      <c r="R33">
+        <v>39.628564838782921</v>
+      </c>
+      <c r="S33">
+        <v>0.98504357722539726</v>
+      </c>
+      <c r="T33">
+        <v>58.174467490963828</v>
+      </c>
+      <c r="U33">
+        <v>1.3362271809132813</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B34">
         <v>25</v>
@@ -915,10 +2490,64 @@
       <c r="C34">
         <v>4</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D34" s="2">
+        <v>34.806666666666665</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0.60500688701313932</v>
+      </c>
+      <c r="F34" s="2">
+        <v>6.66</v>
+      </c>
+      <c r="G34" s="2">
+        <v>4.3588989435406823E-2</v>
+      </c>
+      <c r="H34" s="2">
+        <v>30.526666666666671</v>
+      </c>
+      <c r="I34" s="2">
+        <v>0.85873938615469025</v>
+      </c>
+      <c r="J34">
+        <v>13.575260381644028</v>
+      </c>
+      <c r="K34">
+        <v>0.15097274402385602</v>
+      </c>
+      <c r="L34">
+        <v>8.4523086095600632</v>
+      </c>
+      <c r="M34">
+        <v>0.27951794535153629</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>4.3686192719946435</v>
+      </c>
+      <c r="Q34">
+        <v>0.1653034064185461</v>
+      </c>
+      <c r="R34">
+        <v>29.127017653610523</v>
+      </c>
+      <c r="S34">
+        <v>1.0217490594744201</v>
+      </c>
+      <c r="T34">
+        <v>42.174216088975804</v>
+      </c>
+      <c r="U34">
+        <v>1.4853847503664133</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B35">
         <v>25</v>
@@ -926,10 +2555,64 @@
       <c r="C35">
         <v>5</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D35" s="2">
+        <v>25.66</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0.77149206087943545</v>
+      </c>
+      <c r="F35" s="2">
+        <v>6.8033333333333337</v>
+      </c>
+      <c r="G35" s="2">
+        <v>1.5275252316519626E-2</v>
+      </c>
+      <c r="H35" s="2">
+        <v>22.586666666666662</v>
+      </c>
+      <c r="I35" s="2">
+        <v>0.53482084227648818</v>
+      </c>
+      <c r="J35">
+        <v>10.415714050895831</v>
+      </c>
+      <c r="K35">
+        <v>0.32789825545505907</v>
+      </c>
+      <c r="L35">
+        <v>7.1664736614803699</v>
+      </c>
+      <c r="M35">
+        <v>6.4545636023719821E-2</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>3.353068191620673</v>
+      </c>
+      <c r="Q35">
+        <v>4.2566958725478145E-2</v>
+      </c>
+      <c r="R35">
+        <v>22.075556406324619</v>
+      </c>
+      <c r="S35">
+        <v>0.34789521162487769</v>
+      </c>
+      <c r="T35">
+        <v>32.181265011960299</v>
+      </c>
+      <c r="U35">
+        <v>0.5811283096618558</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B36">
         <v>25</v>
@@ -937,10 +2620,64 @@
       <c r="C36">
         <v>6</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D36" s="2">
+        <v>22.919999999999998</v>
+      </c>
+      <c r="E36" s="2">
+        <v>2.9916049204399213</v>
+      </c>
+      <c r="F36" s="2">
+        <v>7.0566666666666675</v>
+      </c>
+      <c r="G36" s="2">
+        <v>0.20132891827388635</v>
+      </c>
+      <c r="H36" s="2">
+        <v>15.916666666666666</v>
+      </c>
+      <c r="I36" s="2">
+        <v>0.58054572027819906</v>
+      </c>
+      <c r="J36">
+        <v>8.6820280629398852</v>
+      </c>
+      <c r="K36">
+        <v>0.4282777131801962</v>
+      </c>
+      <c r="L36">
+        <v>6.9329182766356716</v>
+      </c>
+      <c r="M36">
+        <v>1.808974068517665</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>2.3223408862937061</v>
+      </c>
+      <c r="Q36">
+        <v>4.1270177420207221E-2</v>
+      </c>
+      <c r="R36">
+        <v>15.446829422594433</v>
+      </c>
+      <c r="S36">
+        <v>0.27374611713366265</v>
+      </c>
+      <c r="T36">
+        <v>22.055264336497288</v>
+      </c>
+      <c r="U36">
+        <v>0.40509356216566011</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B37">
         <v>100</v>
@@ -948,10 +2685,16 @@
       <c r="C37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B38">
         <v>100</v>
@@ -959,10 +2702,70 @@
       <c r="C38">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D38" s="2">
+        <v>63480</v>
+      </c>
+      <c r="E38" s="2">
+        <v>2814.6935890075138</v>
+      </c>
+      <c r="F38" s="2">
+        <v>4.0266666666666664</v>
+      </c>
+      <c r="G38" s="2">
+        <v>1.1547005383792781E-2</v>
+      </c>
+      <c r="H38" s="2">
+        <v>9.31</v>
+      </c>
+      <c r="I38" s="2">
+        <v>0.92601295887260737</v>
+      </c>
+      <c r="J38">
+        <v>16766.666666666668</v>
+      </c>
+      <c r="K38">
+        <v>110.15141094572203</v>
+      </c>
+      <c r="L38">
+        <v>39.922167314476155</v>
+      </c>
+      <c r="M38">
+        <v>5.9066640056853137</v>
+      </c>
+      <c r="N38">
+        <v>35.440715784496263</v>
+      </c>
+      <c r="O38">
+        <v>0.63218765083235684</v>
+      </c>
+      <c r="P38">
+        <v>19.519991310580362</v>
+      </c>
+      <c r="Q38">
+        <v>0.56241958655653879</v>
+      </c>
+      <c r="R38">
+        <v>19.44886697229548</v>
+      </c>
+      <c r="S38">
+        <v>0.59921064222508058</v>
+      </c>
+      <c r="T38">
+        <v>0.33593906022652709</v>
+      </c>
+      <c r="U38">
+        <v>3.1946395189449701E-2</v>
+      </c>
+      <c r="V38">
+        <v>2.5280528052805296</v>
+      </c>
+      <c r="W38">
+        <v>0.17329089891518268</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B39">
         <v>100</v>
@@ -970,10 +2773,67 @@
       <c r="C39">
         <v>2</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D39" s="2">
+        <v>5982</v>
+      </c>
+      <c r="E39" s="2">
+        <v>186.08331467383098</v>
+      </c>
+      <c r="F39" s="2">
+        <v>5.0966666666666667</v>
+      </c>
+      <c r="G39" s="2">
+        <v>7.2341781380702352E-2</v>
+      </c>
+      <c r="H39" s="2">
+        <v>7.5733333333333333</v>
+      </c>
+      <c r="I39" s="2">
+        <v>0.65431898439013159</v>
+      </c>
+      <c r="J39">
+        <v>1220.23971381107</v>
+      </c>
+      <c r="K39">
+        <v>29.841579519435381</v>
+      </c>
+      <c r="L39">
+        <v>3.0194875810170085</v>
+      </c>
+      <c r="M39">
+        <v>0.25468180224459092</v>
+      </c>
+      <c r="N39">
+        <v>0.27011285332299323</v>
+      </c>
+      <c r="O39">
+        <v>4.8494536705360379E-2</v>
+      </c>
+      <c r="P39">
+        <v>0.32159659504820659</v>
+      </c>
+      <c r="Q39">
+        <v>2.7710578056569138E-2</v>
+      </c>
+      <c r="R39">
+        <v>0.28881085826186775</v>
+      </c>
+      <c r="S39">
+        <v>7.1915497078715071E-2</v>
+      </c>
+      <c r="T39">
+        <v>0.76125265089916605</v>
+      </c>
+      <c r="U39">
+        <v>0.13804206468097696</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B40">
         <v>100</v>
@@ -981,10 +2841,64 @@
       <c r="C40">
         <v>3</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D40" s="2">
+        <v>460.23333333333335</v>
+      </c>
+      <c r="E40" s="2">
+        <v>22.893740046862906</v>
+      </c>
+      <c r="F40" s="2">
+        <v>6.04</v>
+      </c>
+      <c r="G40" s="2">
+        <v>1.7320508075688915E-2</v>
+      </c>
+      <c r="H40" s="2">
+        <v>55.74</v>
+      </c>
+      <c r="I40" s="2">
+        <v>1.8594622878671132</v>
+      </c>
+      <c r="J40">
+        <v>98.062338667521658</v>
+      </c>
+      <c r="K40">
+        <v>2.7135355741317353</v>
+      </c>
+      <c r="L40">
+        <v>11.273413822228846</v>
+      </c>
+      <c r="M40">
+        <v>0.44765366894618758</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>6.6859303211517371</v>
+      </c>
+      <c r="Q40">
+        <v>0.19414195111902982</v>
+      </c>
+      <c r="R40">
+        <v>46.374793522065211</v>
+      </c>
+      <c r="S40">
+        <v>1.0727674789434296</v>
+      </c>
+      <c r="T40">
+        <v>68.900937695721908</v>
+      </c>
+      <c r="U40">
+        <v>1.7501467397397272</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B41">
         <v>100</v>
@@ -992,10 +2906,64 @@
       <c r="C41">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D41" s="2">
+        <v>63.713333333333338</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0.7200231477760537</v>
+      </c>
+      <c r="F41" s="2">
+        <v>6.73</v>
+      </c>
+      <c r="G41" s="2">
+        <v>1.0000000000000231E-2</v>
+      </c>
+      <c r="H41" s="2">
+        <v>46.370000000000005</v>
+      </c>
+      <c r="I41" s="2">
+        <v>1.2675961501992641</v>
+      </c>
+      <c r="J41">
+        <v>25.011100237648364</v>
+      </c>
+      <c r="K41">
+        <v>0.52607746756889973</v>
+      </c>
+      <c r="L41">
+        <v>11.233914642023153</v>
+      </c>
+      <c r="M41">
+        <v>0.22523838112561217</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>6.350415299159466</v>
+      </c>
+      <c r="Q41">
+        <v>0.16409869287753398</v>
+      </c>
+      <c r="R41">
+        <v>42.318061369285836</v>
+      </c>
+      <c r="S41">
+        <v>1.2223886713024512</v>
+      </c>
+      <c r="T41">
+        <v>62.074885454559734</v>
+      </c>
+      <c r="U41">
+        <v>1.4873096582941872</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B42">
         <v>100</v>
@@ -1003,10 +2971,64 @@
       <c r="C42">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D42" s="2">
+        <v>32.663333333333334</v>
+      </c>
+      <c r="E42" s="2">
+        <v>1.1123099088533441</v>
+      </c>
+      <c r="F42" s="2">
+        <v>6.9533333333333331</v>
+      </c>
+      <c r="G42" s="2">
+        <v>2.3094010767585053E-2</v>
+      </c>
+      <c r="H42" s="2">
+        <v>27.433333333333334</v>
+      </c>
+      <c r="I42" s="2">
+        <v>0.35725807665234521</v>
+      </c>
+      <c r="J42">
+        <v>13.935237070575752</v>
+      </c>
+      <c r="K42">
+        <v>0.37231709502277988</v>
+      </c>
+      <c r="L42">
+        <v>7.338630465773111</v>
+      </c>
+      <c r="M42">
+        <v>0.2535654882780472</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>3.6404883598359139</v>
+      </c>
+      <c r="Q42">
+        <v>8.8861101258519065E-2</v>
+      </c>
+      <c r="R42">
+        <v>24.266361138700891</v>
+      </c>
+      <c r="S42">
+        <v>0.63273199037536598</v>
+      </c>
+      <c r="T42">
+        <v>34.985736355711943</v>
+      </c>
+      <c r="U42">
+        <v>0.82495976134364735</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B43">
         <v>100</v>
@@ -1014,6 +3036,68 @@
       <c r="C43">
         <v>6</v>
       </c>
+      <c r="D43" s="2">
+        <v>26.103333333333335</v>
+      </c>
+      <c r="E43" s="2">
+        <v>0.69428620419343967</v>
+      </c>
+      <c r="F43" s="2">
+        <v>7.0666666666666664</v>
+      </c>
+      <c r="G43" s="2">
+        <v>9.8149545762236334E-2</v>
+      </c>
+      <c r="H43" s="2">
+        <v>19.36333333333333</v>
+      </c>
+      <c r="I43" s="2">
+        <v>0.8198983676854914</v>
+      </c>
+      <c r="J43">
+        <v>11.093229330105649</v>
+      </c>
+      <c r="K43">
+        <v>0.23854590886209748</v>
+      </c>
+      <c r="L43">
+        <v>6.1895807774478229</v>
+      </c>
+      <c r="M43">
+        <v>0.25361707536797501</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>2.5299317537317325</v>
+      </c>
+      <c r="Q43">
+        <v>0.18198657407738683</v>
+      </c>
+      <c r="R43">
+        <v>16.929603348415068</v>
+      </c>
+      <c r="S43">
+        <v>1.0908852566710516</v>
+      </c>
+      <c r="T43">
+        <v>24.12446056795832</v>
+      </c>
+      <c r="U43">
+        <v>1.7307661197495123</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
